--- a/output/pdf_financials_xlsx/UGD.xlsx
+++ b/output/pdf_financials_xlsx/UGD.xlsx
@@ -1323,19 +1323,19 @@
         <v>-1.052465</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>7.445949</v>
+        <v>-7.445949</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>6.378144</v>
+        <v>-6.378144</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>3.172666</v>
+        <v>-3.172666</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>2.326711</v>
+        <v>-2.326711</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>2.547613</v>
+        <v>-2.547613</v>
       </c>
     </row>
     <row r="17">
@@ -1627,19 +1627,19 @@
         <v>-1.052465</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>7.445949</v>
+        <v>-7.445949</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>6.378144</v>
+        <v>-6.378144</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>3.172666</v>
+        <v>-3.172666</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.326711</v>
+        <v>-2.326711</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2.547613</v>
+        <v>-2.547613</v>
       </c>
     </row>
     <row r="21">
@@ -1805,19 +1805,19 @@
         <v>-1.052465</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>7.445949</v>
+        <v>-7.445949</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>6.378144</v>
+        <v>-6.378144</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.172666</v>
+        <v>-3.172666</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>2.326711</v>
+        <v>-2.326711</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>2.547613</v>
+        <v>-2.547613</v>
       </c>
     </row>
     <row r="24">
@@ -2009,10 +2009,10 @@
         <v>52.62325</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>148.91898</v>
+        <v>-148.91898</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>212.6048</v>
+        <v>-212.6048</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -2075,19 +2075,19 @@
         <v>-1.052465</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>7.445949</v>
+        <v>-7.445949</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>6.378144</v>
+        <v>-6.378144</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>3.172666</v>
+        <v>-3.172666</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>2.326711</v>
+        <v>-2.326711</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.547613</v>
+        <v>-2.547613</v>
       </c>
     </row>
     <row r="28">
@@ -2195,19 +2195,19 @@
         <v>-1.052465</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>7.445949</v>
+        <v>-7.445949</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>6.378144</v>
+        <v>-6.378144</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>3.333622</v>
+        <v>-3.01171</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.4644</v>
+        <v>-2.189022</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.665278</v>
+        <v>-2.429948</v>
       </c>
     </row>
     <row r="30">
@@ -2347,19 +2347,19 @@
         <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5992,43 +5992,43 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.348996</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.374178</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.389382</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.09908</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.249939</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.150859</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.990736</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.482966</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.883971</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.623324</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.676319</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.942335</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.042488</v>
       </c>
     </row>
     <row r="93">
@@ -6377,19 +6377,19 @@
         <v>-1.052465</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>7.445949</v>
+        <v>-7.445949</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>6.378144</v>
+        <v>-6.378144</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>3.172666</v>
+        <v>-3.172666</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>2.326711</v>
+        <v>-2.326711</v>
       </c>
       <c r="R99" s="3" t="n">
-        <v>2.547613</v>
+        <v>-2.547613</v>
       </c>
     </row>
     <row r="100">
@@ -9492,7 +9492,11 @@
           <t>Reserve for warrants 8(b)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -12878,7 +12882,11 @@
           <t>Reserve for warrants 7(b)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -15628,7 +15636,11 @@
           <t>Reserve for warrants (Note 8(b))</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -17325,7 +17337,11 @@
           <t>Reserve for warrants (Note 8(b))</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -38232,19 +38248,19 @@
         </is>
       </c>
       <c r="Q301" s="5" t="n">
-        <v>7.445949</v>
+        <v>-7.445949</v>
       </c>
       <c r="R301" s="5" t="n">
-        <v>6.378144</v>
+        <v>-6.378144</v>
       </c>
       <c r="S301" s="5" t="n">
-        <v>3.172666</v>
+        <v>-3.172666</v>
       </c>
       <c r="T301" s="5" t="n">
-        <v>2.326711</v>
+        <v>-2.326711</v>
       </c>
       <c r="U301" s="5" t="n">
-        <v>2.547613</v>
+        <v>-2.547613</v>
       </c>
     </row>
     <row r="302">

--- a/output/pdf_financials_xlsx/UGD.xlsx
+++ b/output/pdf_financials_xlsx/UGD.xlsx
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.404312</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>143.056</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>22.557</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007219</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00241</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.268479</v>
+        <v>-3.672791</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1150.329</v>
+        <v>-1293.385</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2670.766</v>
+        <v>-2693.323</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
         <v>-1.052465</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-7.445949</v>
+        <v>-7.43873</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-6.378144</v>
+        <v>-6.375734</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-3.172666</v>
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.268479</v>
+        <v>-3.672791</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1150.329</v>
+        <v>-1293.385</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2670.766</v>
+        <v>-2693.323</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>-1.052465</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-7.445949</v>
+        <v>-7.43873</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-6.378144</v>
+        <v>-6.375734</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-3.01171</v>
@@ -2468,55 +2468,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.172185</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>9845.49</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3449.396</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.540945</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>8.265454</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>5.015425</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.63885</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.596348</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.594593</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.453259</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.549412</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.37221</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.003939</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.252646</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.825738</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.149607</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.363419</v>
       </c>
     </row>
     <row r="35">
@@ -2584,55 +2584,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.172185</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>9845.49</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3449.396</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.540945</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>8.265454</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>5.015425</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.63885</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.596348</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.594593</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.453259</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.549412</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.37221</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.003939</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.252646</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.825738</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.149607</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.363419</v>
       </c>
     </row>
     <row r="37">
@@ -3280,55 +3280,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.651551</v>
+        <v>0.479366</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>9946.602000000001</v>
+        <v>101.112</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3569.009</v>
+        <v>119.613</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.598033</v>
+        <v>0.057088</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8.516778</v>
+        <v>0.251324</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5.097347</v>
+        <v>0.08192199999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.676173</v>
+        <v>0.037323</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.620291</v>
+        <v>0.023943</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.614</v>
+        <v>0.019407</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.471638</v>
+        <v>0.018379</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.5717989999999999</v>
+        <v>0.022387</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.440459</v>
+        <v>0.068249</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.119737</v>
+        <v>0.115798</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.314029</v>
+        <v>0.061383</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.911317</v>
+        <v>0.085579</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.245517</v>
+        <v>0.09591</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.415934</v>
+        <v>0.052515</v>
       </c>
     </row>
     <row r="49">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -40049,7 +40049,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -41682,7 +41682,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E337" s="5" t="n">
@@ -42686,7 +42686,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E347" s="5" t="n">

--- a/output/pdf_financials_xlsx/UGD.xlsx
+++ b/output/pdf_financials_xlsx/UGD.xlsx
@@ -751,7 +751,7 @@
         <v>168.751</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>177.184</v>
+        <v>281.818</v>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
@@ -6841,19 +6841,19 @@
         <v>0.311301</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.279248</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.116907</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.148919</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.016899</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>0.310399</v>
       </c>
     </row>
     <row r="108">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-103.402</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>-0.027357</v>
@@ -8421,7 +8421,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-103.402</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>-0.027357</v>
@@ -8479,7 +8479,7 @@
         <v>-666.682</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1324.493</v>
+        <v>-1427.895</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.847231</v>
@@ -25762,7 +25762,11 @@
           <t>Share-based compensation expense 8(c)</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -28027,7 +28031,11 @@
           <t>Share-based compensation expense 7(c)</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -31178,7 +31186,11 @@
           <t>Private placement (Note 8(a))</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -32481,7 +32493,11 @@
           <t>Private placement (Note 10a)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -34000,7 +34016,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -41781,7 +41801,11 @@
           <t>Salaries and directors’ fees</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
